--- a/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
+++ b/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF36D7D-5F1A-5A4E-BB4F-A1A0775D03D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F93AB4-24DA-E445-9D88-9AED553DB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -380,6 +380,12 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>https://bikepacking.com/bikes/santa-cruz-stigmata-review/</t>
   </si>
 </sst>
 </file>
@@ -1461,12 +1467,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -1474,7 +1480,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>75</v>
       </c>
@@ -1482,7 +1488,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1490,12 +1496,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -1527,12 +1533,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -1540,27 +1546,36 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>94</v>
       </c>

--- a/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
+++ b/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F93AB4-24DA-E445-9D88-9AED553DB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38760FE8-725D-604C-99FE-E12F57B32DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30920" yWindow="-17800" windowWidth="26480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>https://bikepacking.com/bikes/santa-cruz-stigmata-review/</t>
+  </si>
+  <si>
+    <t>https://www.santacruzbicycles.com/cdn/shop/files/MY26_Stigmata_CC_FORCE_1X_AXS_RSV_RUDY_BritishRacingGreen_8692d437-33a5-4167-89ba-dabaee544268.png?crop=region&amp;crop_height=2007&amp;crop_left=51&amp;crop_top=220&amp;crop_width=3096&amp;v=1755206810&amp;width=1388</t>
   </si>
 </sst>
 </file>
@@ -770,6 +773,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>

--- a/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
+++ b/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38760FE8-725D-604C-99FE-E12F57B32DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEA834E-DCEA-CE41-9581-46DB65F18A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30920" yWindow="-17800" windowWidth="26480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="1060" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -352,9 +352,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>crank_length</t>
   </si>
   <si>
@@ -389,6 +386,15 @@
   </si>
   <si>
     <t>https://www.santacruzbicycles.com/cdn/shop/files/MY26_Stigmata_CC_FORCE_1X_AXS_RSV_RUDY_BritishRacingGreen_8692d437-33a5-4167-89ba-dabaee544268.png?crop=region&amp;crop_height=2007&amp;crop_left=51&amp;crop_top=220&amp;crop_width=3096&amp;v=1755206810&amp;width=1388</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -775,7 +781,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -783,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1224,7 +1230,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1262,7 +1268,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1398,26 +1404,26 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" t="s">
         <v>114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s">
         <v>116</v>
-      </c>
-      <c r="B39" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
-      </c>
-      <c r="B40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1564,7 +1570,7 @@
         <v>91</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1572,10 +1578,10 @@
         <v>92</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" t="s">
         <v>120</v>
-      </c>
-      <c r="C62" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1663,8 +1669,16 @@
       <c r="A75" t="s">
         <v>109</v>
       </c>
-      <c r="B75" t="s">
-        <v>110</v>
+      <c r="B75" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>122</v>
+      </c>
+      <c r="B76" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
+++ b/data/gravel/Santa Cruz Stigmata CC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEA834E-DCEA-CE41-9581-46DB65F18A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50135003-A09A-6F40-AA65-5BDF038A88E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="1060" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -395,6 +395,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -733,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1481,12 +1499,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -1494,7 +1512,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>75</v>
       </c>
@@ -1502,182 +1520,212 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>77</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B58" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>80</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B60" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>82</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B61" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>83</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B62" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>85</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>88</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B65" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C68" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>94</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B70" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>95</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B71" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>97</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B72" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>99</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B73" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>101</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B75" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>104</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>109</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>122</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>123</v>
       </c>
     </row>
